--- a/data/test/addresses.xlsx
+++ b/data/test/addresses.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I64"/>
+  <dimension ref="A1:I65"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -454,7 +454,7 @@
         <v>106.7033</v>
       </c>
       <c r="I2" t="str">
-        <v>2026-05-08T18:17:00.349Z</v>
+        <v>2026-05-09T04:27:53.251Z</v>
       </c>
     </row>
     <row r="3">
@@ -483,7 +483,7 @@
         <v>106.7071</v>
       </c>
       <c r="I3" t="str">
-        <v>2026-05-08T18:17:00.349Z</v>
+        <v>2026-05-09T04:27:53.251Z</v>
       </c>
     </row>
     <row r="4">
@@ -512,7 +512,7 @@
         <v>106.6981</v>
       </c>
       <c r="I4" t="str">
-        <v>2026-05-08T18:17:00.349Z</v>
+        <v>2026-05-09T04:27:53.251Z</v>
       </c>
     </row>
     <row r="5">
@@ -541,7 +541,7 @@
         <v>106.7009</v>
       </c>
       <c r="I5" t="str">
-        <v>2026-05-08T18:17:00.349Z</v>
+        <v>2026-05-09T04:27:53.251Z</v>
       </c>
     </row>
     <row r="6">
@@ -570,7 +570,7 @@
         <v>106.6961</v>
       </c>
       <c r="I6" t="str">
-        <v>2026-05-08T18:17:00.349Z</v>
+        <v>2026-05-09T04:27:53.251Z</v>
       </c>
     </row>
     <row r="7">
@@ -599,7 +599,7 @@
         <v>106.7012</v>
       </c>
       <c r="I7" t="str">
-        <v>2026-05-08T18:17:00.349Z</v>
+        <v>2026-05-09T04:27:53.251Z</v>
       </c>
     </row>
     <row r="8">
@@ -628,7 +628,7 @@
         <v>106.63</v>
       </c>
       <c r="I8" t="str">
-        <v>2026-05-08T18:17:00.349Z</v>
+        <v>2026-05-09T04:27:53.251Z</v>
       </c>
     </row>
     <row r="9">
@@ -657,7 +657,7 @@
         <v>106.6892</v>
       </c>
       <c r="I9" t="str">
-        <v>2026-05-08T18:17:00.349Z</v>
+        <v>2026-05-09T04:27:53.251Z</v>
       </c>
     </row>
     <row r="10">
@@ -686,7 +686,7 @@
         <v>106.6878</v>
       </c>
       <c r="I10" t="str">
-        <v>2026-05-08T18:17:00.349Z</v>
+        <v>2026-05-09T04:27:53.251Z</v>
       </c>
     </row>
     <row r="11">
@@ -715,7 +715,7 @@
         <v>106.693</v>
       </c>
       <c r="I11" t="str">
-        <v>2026-05-08T18:17:00.349Z</v>
+        <v>2026-05-09T04:27:53.251Z</v>
       </c>
     </row>
     <row r="12">
@@ -744,7 +744,7 @@
         <v>106.7052</v>
       </c>
       <c r="I12" t="str">
-        <v>2026-05-08T18:17:00.349Z</v>
+        <v>2026-05-09T04:27:53.251Z</v>
       </c>
     </row>
     <row r="13">
@@ -773,7 +773,7 @@
         <v>106.705</v>
       </c>
       <c r="I13" t="str">
-        <v>2026-05-08T18:17:00.349Z</v>
+        <v>2026-05-09T04:27:53.251Z</v>
       </c>
     </row>
     <row r="14">
@@ -802,7 +802,7 @@
         <v>106.7018</v>
       </c>
       <c r="I14" t="str">
-        <v>2026-05-08T18:17:00.349Z</v>
+        <v>2026-05-09T04:27:53.251Z</v>
       </c>
     </row>
     <row r="15">
@@ -831,7 +831,7 @@
         <v>106.6844</v>
       </c>
       <c r="I15" t="str">
-        <v>2026-05-08T18:17:00.349Z</v>
+        <v>2026-05-09T04:27:53.251Z</v>
       </c>
     </row>
     <row r="16">
@@ -860,7 +860,7 @@
         <v>106.684</v>
       </c>
       <c r="I16" t="str">
-        <v>2026-05-08T18:17:00.349Z</v>
+        <v>2026-05-09T04:27:53.251Z</v>
       </c>
     </row>
     <row r="17">
@@ -889,7 +889,7 @@
         <v>106.6803</v>
       </c>
       <c r="I17" t="str">
-        <v>2026-05-08T18:17:00.349Z</v>
+        <v>2026-05-09T04:27:53.251Z</v>
       </c>
     </row>
     <row r="18">
@@ -918,7 +918,7 @@
         <v>106.6411</v>
       </c>
       <c r="I18" t="str">
-        <v>2026-05-08T18:17:00.349Z</v>
+        <v>2026-05-09T04:27:53.251Z</v>
       </c>
     </row>
     <row r="19">
@@ -947,7 +947,7 @@
         <v>106.6762</v>
       </c>
       <c r="I19" t="str">
-        <v>2026-05-08T18:17:00.349Z</v>
+        <v>2026-05-09T04:27:53.251Z</v>
       </c>
     </row>
     <row r="20">
@@ -976,7 +976,7 @@
         <v>106.7098</v>
       </c>
       <c r="I20" t="str">
-        <v>2026-05-08T18:17:00.349Z</v>
+        <v>2026-05-09T04:27:53.251Z</v>
       </c>
     </row>
     <row r="21">
@@ -1005,7 +1005,7 @@
         <v>106.7122</v>
       </c>
       <c r="I21" t="str">
-        <v>2026-05-08T18:17:00.349Z</v>
+        <v>2026-05-09T04:27:53.251Z</v>
       </c>
     </row>
     <row r="22">
@@ -1034,7 +1034,7 @@
         <v>106.7199</v>
       </c>
       <c r="I22" t="str">
-        <v>2026-05-08T18:17:00.349Z</v>
+        <v>2026-05-09T04:27:53.251Z</v>
       </c>
     </row>
     <row r="23">
@@ -1063,7 +1063,7 @@
         <v>106.7221</v>
       </c>
       <c r="I23" t="str">
-        <v>2026-05-08T18:17:00.349Z</v>
+        <v>2026-05-09T04:27:53.251Z</v>
       </c>
     </row>
     <row r="24">
@@ -1092,7 +1092,7 @@
         <v>106.7</v>
       </c>
       <c r="I24" t="str">
-        <v>2026-05-08T18:17:00.349Z</v>
+        <v>2026-05-09T04:27:53.251Z</v>
       </c>
     </row>
     <row r="25">
@@ -1121,7 +1121,7 @@
         <v>106.7012</v>
       </c>
       <c r="I25" t="str">
-        <v>2026-05-08T18:17:00.349Z</v>
+        <v>2026-05-09T04:27:53.251Z</v>
       </c>
     </row>
     <row r="26">
@@ -1150,7 +1150,7 @@
         <v>106.71</v>
       </c>
       <c r="I26" t="str">
-        <v>2026-05-08T18:17:00.349Z</v>
+        <v>2026-05-09T04:27:53.251Z</v>
       </c>
     </row>
     <row r="27">
@@ -1179,7 +1179,7 @@
         <v>106.7071</v>
       </c>
       <c r="I27" t="str">
-        <v>2026-05-08T18:17:00.349Z</v>
+        <v>2026-05-09T04:27:53.251Z</v>
       </c>
     </row>
     <row r="28">
@@ -1208,7 +1208,7 @@
         <v>106.7033</v>
       </c>
       <c r="I28" t="str">
-        <v>2026-05-08T18:17:00.349Z</v>
+        <v>2026-05-09T04:27:53.251Z</v>
       </c>
     </row>
     <row r="29">
@@ -1237,7 +1237,7 @@
         <v>106.6905</v>
       </c>
       <c r="I29" t="str">
-        <v>2026-05-08T18:17:00.349Z</v>
+        <v>2026-05-09T04:27:53.251Z</v>
       </c>
     </row>
     <row r="30">
@@ -1266,7 +1266,7 @@
         <v>106.6522</v>
       </c>
       <c r="I30" t="str">
-        <v>2026-05-08T18:17:00.349Z</v>
+        <v>2026-05-09T04:27:53.251Z</v>
       </c>
     </row>
     <row r="31">
@@ -1295,7 +1295,7 @@
         <v>106.6478</v>
       </c>
       <c r="I31" t="str">
-        <v>2026-05-08T18:17:00.349Z</v>
+        <v>2026-05-09T04:27:53.251Z</v>
       </c>
     </row>
     <row r="32">
@@ -1324,7 +1324,7 @@
         <v>106.63</v>
       </c>
       <c r="I32" t="str">
-        <v>2026-05-08T18:17:00.349Z</v>
+        <v>2026-05-09T04:27:53.251Z</v>
       </c>
     </row>
     <row r="33">
@@ -1353,7 +1353,7 @@
         <v>106.7012</v>
       </c>
       <c r="I33" t="str">
-        <v>2026-05-08T18:17:00.349Z</v>
+        <v>2026-05-09T04:27:53.251Z</v>
       </c>
     </row>
     <row r="34">
@@ -1382,7 +1382,7 @@
         <v>106.6832</v>
       </c>
       <c r="I34" t="str">
-        <v>2026-05-08T18:17:00.349Z</v>
+        <v>2026-05-09T04:27:53.251Z</v>
       </c>
     </row>
     <row r="35">
@@ -1411,7 +1411,7 @@
         <v>106.6889</v>
       </c>
       <c r="I35" t="str">
-        <v>2026-05-08T18:17:00.349Z</v>
+        <v>2026-05-09T04:27:53.251Z</v>
       </c>
     </row>
     <row r="36">
@@ -1440,7 +1440,7 @@
         <v>106.6811</v>
       </c>
       <c r="I36" t="str">
-        <v>2026-05-08T18:17:00.349Z</v>
+        <v>2026-05-09T04:27:53.251Z</v>
       </c>
     </row>
     <row r="37">
@@ -1469,7 +1469,7 @@
         <v>106.705</v>
       </c>
       <c r="I37" t="str">
-        <v>2026-05-08T18:17:00.349Z</v>
+        <v>2026-05-09T04:27:53.251Z</v>
       </c>
     </row>
     <row r="38">
@@ -1498,7 +1498,7 @@
         <v>106.7052</v>
       </c>
       <c r="I38" t="str">
-        <v>2026-05-08T18:17:00.349Z</v>
+        <v>2026-05-09T04:27:53.251Z</v>
       </c>
     </row>
     <row r="39">
@@ -1527,7 +1527,7 @@
         <v>106.712</v>
       </c>
       <c r="I39" t="str">
-        <v>2026-05-08T18:17:00.349Z</v>
+        <v>2026-05-09T04:27:53.251Z</v>
       </c>
     </row>
     <row r="40">
@@ -1556,7 +1556,7 @@
         <v>106.638</v>
       </c>
       <c r="I40" t="str">
-        <v>2026-05-08T18:17:00.349Z</v>
+        <v>2026-05-09T04:27:53.251Z</v>
       </c>
     </row>
     <row r="41">
@@ -1585,7 +1585,7 @@
         <v>106.642</v>
       </c>
       <c r="I41" t="str">
-        <v>2026-05-08T18:17:00.349Z</v>
+        <v>2026-05-09T04:27:53.251Z</v>
       </c>
     </row>
     <row r="42">
@@ -1614,7 +1614,7 @@
         <v>106.6411</v>
       </c>
       <c r="I42" t="str">
-        <v>2026-05-08T18:17:00.349Z</v>
+        <v>2026-05-09T04:27:53.251Z</v>
       </c>
     </row>
     <row r="43">
@@ -1643,7 +1643,7 @@
         <v>106.6803</v>
       </c>
       <c r="I43" t="str">
-        <v>2026-05-08T18:17:00.349Z</v>
+        <v>2026-05-09T04:27:53.251Z</v>
       </c>
     </row>
     <row r="44">
@@ -1672,7 +1672,7 @@
         <v>106.653</v>
       </c>
       <c r="I44" t="str">
-        <v>2026-05-08T18:17:00.349Z</v>
+        <v>2026-05-09T04:27:53.251Z</v>
       </c>
     </row>
     <row r="45">
@@ -1701,7 +1701,7 @@
         <v>106.772</v>
       </c>
       <c r="I45" t="str">
-        <v>2026-05-08T18:17:00.349Z</v>
+        <v>2026-05-09T04:27:53.251Z</v>
       </c>
     </row>
     <row r="46">
@@ -1730,7 +1730,7 @@
         <v>106.7601</v>
       </c>
       <c r="I46" t="str">
-        <v>2026-05-08T18:17:00.349Z</v>
+        <v>2026-05-09T04:27:53.251Z</v>
       </c>
     </row>
     <row r="47">
@@ -1759,7 +1759,7 @@
         <v>106.7221</v>
       </c>
       <c r="I47" t="str">
-        <v>2026-05-08T18:17:00.349Z</v>
+        <v>2026-05-09T04:27:53.251Z</v>
       </c>
     </row>
     <row r="48">
@@ -1788,7 +1788,7 @@
         <v>106.7199</v>
       </c>
       <c r="I48" t="str">
-        <v>2026-05-08T18:17:00.349Z</v>
+        <v>2026-05-09T04:27:53.251Z</v>
       </c>
     </row>
     <row r="49">
@@ -1817,7 +1817,7 @@
         <v>106.702</v>
       </c>
       <c r="I49" t="str">
-        <v>2026-05-08T18:17:00.349Z</v>
+        <v>2026-05-09T04:27:53.251Z</v>
       </c>
     </row>
     <row r="50">
@@ -1846,7 +1846,7 @@
         <v>106.605</v>
       </c>
       <c r="I50" t="str">
-        <v>2026-05-08T18:17:00.349Z</v>
+        <v>2026-05-09T04:27:53.251Z</v>
       </c>
     </row>
     <row r="51">
@@ -1875,7 +1875,7 @@
         <v>106.6</v>
       </c>
       <c r="I51" t="str">
-        <v>2026-05-08T18:17:00.349Z</v>
+        <v>2026-05-09T04:27:53.251Z</v>
       </c>
     </row>
     <row r="52">
@@ -1904,7 +1904,7 @@
         <v>106.7033</v>
       </c>
       <c r="I52" t="str">
-        <v>2026-05-08T18:17:00.349Z</v>
+        <v>2026-05-09T04:27:53.251Z</v>
       </c>
     </row>
     <row r="53">
@@ -1933,7 +1933,7 @@
         <v>106.7071</v>
       </c>
       <c r="I53" t="str">
-        <v>2026-05-08T18:17:00.349Z</v>
+        <v>2026-05-09T04:27:53.251Z</v>
       </c>
     </row>
     <row r="54">
@@ -1962,7 +1962,7 @@
         <v>106.6981</v>
       </c>
       <c r="I54" t="str">
-        <v>2026-05-08T18:17:00.349Z</v>
+        <v>2026-05-09T04:27:53.251Z</v>
       </c>
     </row>
     <row r="55">
@@ -1991,7 +1991,7 @@
         <v>106.7009</v>
       </c>
       <c r="I55" t="str">
-        <v>2026-05-08T18:17:00.349Z</v>
+        <v>2026-05-09T04:27:53.251Z</v>
       </c>
     </row>
     <row r="56">
@@ -2020,7 +2020,7 @@
         <v>106.6961</v>
       </c>
       <c r="I56" t="str">
-        <v>2026-05-08T18:17:00.349Z</v>
+        <v>2026-05-09T04:27:53.251Z</v>
       </c>
     </row>
     <row r="57">
@@ -2049,7 +2049,7 @@
         <v>106.7012</v>
       </c>
       <c r="I57" t="str">
-        <v>2026-05-08T18:17:00.349Z</v>
+        <v>2026-05-09T04:27:53.251Z</v>
       </c>
     </row>
     <row r="58">
@@ -2078,7 +2078,7 @@
         <v>106.63</v>
       </c>
       <c r="I58" t="str">
-        <v>2026-05-08T18:17:00.349Z</v>
+        <v>2026-05-09T04:27:53.251Z</v>
       </c>
     </row>
     <row r="59">
@@ -2107,7 +2107,7 @@
         <v>106.6892</v>
       </c>
       <c r="I59" t="str">
-        <v>2026-05-08T18:17:00.349Z</v>
+        <v>2026-05-09T04:27:53.251Z</v>
       </c>
     </row>
     <row r="60">
@@ -2136,7 +2136,7 @@
         <v>106.6878</v>
       </c>
       <c r="I60" t="str">
-        <v>2026-05-08T18:17:00.349Z</v>
+        <v>2026-05-09T04:27:53.251Z</v>
       </c>
     </row>
     <row r="61">
@@ -2165,7 +2165,7 @@
         <v>106.693</v>
       </c>
       <c r="I61" t="str">
-        <v>2026-05-08T18:17:00.349Z</v>
+        <v>2026-05-09T04:27:53.251Z</v>
       </c>
     </row>
     <row r="62">
@@ -2194,7 +2194,7 @@
         <v>106.7052</v>
       </c>
       <c r="I62" t="str">
-        <v>2026-05-08T18:17:00.349Z</v>
+        <v>2026-05-09T04:27:53.251Z</v>
       </c>
     </row>
     <row r="63">
@@ -2223,7 +2223,7 @@
         <v>106.705</v>
       </c>
       <c r="I63" t="str">
-        <v>2026-05-08T18:17:00.349Z</v>
+        <v>2026-05-09T04:27:53.251Z</v>
       </c>
     </row>
     <row r="64">
@@ -2252,12 +2252,41 @@
         <v>106.7018</v>
       </c>
       <c r="I64" t="str">
-        <v>2026-05-08T18:17:00.349Z</v>
+        <v>2026-05-09T04:27:53.251Z</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>e0b99ce7-906b-4dd8-88a6-9afed6432134</v>
+      </c>
+      <c r="B65" t="str">
+        <v>0368980079</v>
+      </c>
+      <c r="C65" t="str">
+        <v>Home</v>
+      </c>
+      <c r="D65" t="str">
+        <v>354 Lý Thường Kiệt</v>
+      </c>
+      <c r="E65" t="str">
+        <v>Q10</v>
+      </c>
+      <c r="F65" t="b">
+        <v>1</v>
+      </c>
+      <c r="G65">
+        <v>10.775595647737902</v>
+      </c>
+      <c r="H65">
+        <v>106.65752279721085</v>
+      </c>
+      <c r="I65" t="str">
+        <v>2026-05-09T04:30:55.379Z</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I64"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I65"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/test/addresses.xlsx
+++ b/data/test/addresses.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I64"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -430,36 +430,1834 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>9db3f6bc-0f19-4ba9-bf42-fb296130ae95</v>
+        <v>test-addr-0901000001-0</v>
       </c>
       <c r="B2" t="str">
-        <v>123498712</v>
+        <v>0901000001</v>
       </c>
       <c r="C2" t="str">
         <v>Home</v>
       </c>
       <c r="D2" t="str">
-        <v>354 Ly Thuong Kiet</v>
+        <v>12 Nguyễn Huệ, Bến Nghé, Quận 1</v>
       </c>
       <c r="E2" t="str">
-        <v>Q10</v>
+        <v>Q1</v>
       </c>
       <c r="F2" t="b">
         <v>1</v>
       </c>
       <c r="G2">
-        <v>10.775863071330383</v>
+        <v>10.7737</v>
       </c>
       <c r="H2">
-        <v>106.65824995248735</v>
+        <v>106.7033</v>
       </c>
       <c r="I2" t="str">
-        <v>2026-05-10T01:34:16.865Z</v>
+        <v>2026-05-12T08:41:15.945Z</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>test-addr-0901000001-1</v>
+      </c>
+      <c r="B3" t="str">
+        <v>0901000001</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Office</v>
+      </c>
+      <c r="D3" t="str">
+        <v>5 Lê Thánh Tôn, Phường Bến Nghé, Quận 1</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Q1</v>
+      </c>
+      <c r="F3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>10.776</v>
+      </c>
+      <c r="H3">
+        <v>106.7071</v>
+      </c>
+      <c r="I3" t="str">
+        <v>2026-05-12T08:41:15.945Z</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>test-addr-0901000002-0</v>
+      </c>
+      <c r="B4" t="str">
+        <v>0901000002</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Home</v>
+      </c>
+      <c r="D4" t="str">
+        <v>56 Lê Lợi, Phường Bến Thành, Quận 1</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Q1</v>
+      </c>
+      <c r="F4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>10.7726</v>
+      </c>
+      <c r="H4">
+        <v>106.6981</v>
+      </c>
+      <c r="I4" t="str">
+        <v>2026-05-12T08:41:15.945Z</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>test-addr-0901000003-0</v>
+      </c>
+      <c r="B5" t="str">
+        <v>0901000003</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Home</v>
+      </c>
+      <c r="D5" t="str">
+        <v>78 Đinh Tiên Hoàng, Phường Đa Kao, Quận 1</v>
+      </c>
+      <c r="E5" t="str">
+        <v>Q1</v>
+      </c>
+      <c r="F5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>10.7869</v>
+      </c>
+      <c r="H5">
+        <v>106.7009</v>
+      </c>
+      <c r="I5" t="str">
+        <v>2026-05-12T08:41:15.945Z</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>test-addr-0901000004-0</v>
+      </c>
+      <c r="B6" t="str">
+        <v>0901000004</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Home</v>
+      </c>
+      <c r="D6" t="str">
+        <v>34 Trần Hưng Đạo, Phường Nguyễn Cư Trinh, Quận 1</v>
+      </c>
+      <c r="E6" t="str">
+        <v>Q1</v>
+      </c>
+      <c r="F6" t="b">
+        <v>1</v>
+      </c>
+      <c r="G6">
+        <v>10.766</v>
+      </c>
+      <c r="H6">
+        <v>106.6961</v>
+      </c>
+      <c r="I6" t="str">
+        <v>2026-05-12T08:41:15.945Z</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>test-addr-0901000005-0</v>
+      </c>
+      <c r="B7" t="str">
+        <v>0901000005</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Home</v>
+      </c>
+      <c r="D7" t="str">
+        <v>101 Lý Tự Trọng, Phường Bến Nghé, Quận 1</v>
+      </c>
+      <c r="E7" t="str">
+        <v>Q1</v>
+      </c>
+      <c r="F7" t="b">
+        <v>1</v>
+      </c>
+      <c r="G7">
+        <v>10.7752</v>
+      </c>
+      <c r="H7">
+        <v>106.7012</v>
+      </c>
+      <c r="I7" t="str">
+        <v>2026-05-12T08:41:15.945Z</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>test-addr-0901000005-1</v>
+      </c>
+      <c r="B8" t="str">
+        <v>0901000005</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Office</v>
+      </c>
+      <c r="D8" t="str">
+        <v>44 Lê Trọng Tấn, Phường Tây Thạnh, Tân Phú</v>
+      </c>
+      <c r="E8" t="str">
+        <v>TP</v>
+      </c>
+      <c r="F8" t="b">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>10.79</v>
+      </c>
+      <c r="H8">
+        <v>106.63</v>
+      </c>
+      <c r="I8" t="str">
+        <v>2026-05-12T08:41:15.945Z</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>test-addr-0901000006-0</v>
+      </c>
+      <c r="B9" t="str">
+        <v>0901000006</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Home</v>
+      </c>
+      <c r="D9" t="str">
+        <v>22 Võ Thị Sáu, Phường 7, Quận 3</v>
+      </c>
+      <c r="E9" t="str">
+        <v>Q3</v>
+      </c>
+      <c r="F9" t="b">
+        <v>1</v>
+      </c>
+      <c r="G9">
+        <v>10.7845</v>
+      </c>
+      <c r="H9">
+        <v>106.6892</v>
+      </c>
+      <c r="I9" t="str">
+        <v>2026-05-12T08:41:15.945Z</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>test-addr-0901000007-0</v>
+      </c>
+      <c r="B10" t="str">
+        <v>0901000007</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Home</v>
+      </c>
+      <c r="D10" t="str">
+        <v>88 Nam Kỳ Khởi Nghĩa, Phường 8, Quận 3</v>
+      </c>
+      <c r="E10" t="str">
+        <v>Q3</v>
+      </c>
+      <c r="F10" t="b">
+        <v>1</v>
+      </c>
+      <c r="G10">
+        <v>10.7804</v>
+      </c>
+      <c r="H10">
+        <v>106.6878</v>
+      </c>
+      <c r="I10" t="str">
+        <v>2026-05-12T08:41:15.945Z</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>test-addr-0901000008-0</v>
+      </c>
+      <c r="B11" t="str">
+        <v>0901000008</v>
+      </c>
+      <c r="C11" t="str">
+        <v>Home</v>
+      </c>
+      <c r="D11" t="str">
+        <v>15 Nguyễn Đình Chiểu, Phường 1, Quận 3</v>
+      </c>
+      <c r="E11" t="str">
+        <v>Q3</v>
+      </c>
+      <c r="F11" t="b">
+        <v>1</v>
+      </c>
+      <c r="G11">
+        <v>10.7763</v>
+      </c>
+      <c r="H11">
+        <v>106.693</v>
+      </c>
+      <c r="I11" t="str">
+        <v>2026-05-12T08:41:15.945Z</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>test-addr-0901000009-0</v>
+      </c>
+      <c r="B12" t="str">
+        <v>0901000009</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Home</v>
+      </c>
+      <c r="D12" t="str">
+        <v>30 Tôn Đức Thắng, Bến Nghé, Quận 1</v>
+      </c>
+      <c r="E12" t="str">
+        <v>Q1</v>
+      </c>
+      <c r="F12" t="b">
+        <v>1</v>
+      </c>
+      <c r="G12">
+        <v>10.7714</v>
+      </c>
+      <c r="H12">
+        <v>106.7052</v>
+      </c>
+      <c r="I12" t="str">
+        <v>2026-05-12T08:41:15.945Z</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>test-addr-0901000009-1</v>
+      </c>
+      <c r="B13" t="str">
+        <v>0901000009</v>
+      </c>
+      <c r="C13" t="str">
+        <v>Office</v>
+      </c>
+      <c r="D13" t="str">
+        <v>15 Nguyễn Thị Thập, Phường Tân Phú, Quận 7</v>
+      </c>
+      <c r="E13" t="str">
+        <v>Q7</v>
+      </c>
+      <c r="F13" t="b">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>10.731</v>
+      </c>
+      <c r="H13">
+        <v>106.705</v>
+      </c>
+      <c r="I13" t="str">
+        <v>2026-05-12T08:41:15.945Z</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>test-addr-0901000010-0</v>
+      </c>
+      <c r="B14" t="str">
+        <v>0901000010</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Home</v>
+      </c>
+      <c r="D14" t="str">
+        <v>8 Hai Bà Trưng, Bến Nghé, Quận 1</v>
+      </c>
+      <c r="E14" t="str">
+        <v>Q1</v>
+      </c>
+      <c r="F14" t="b">
+        <v>1</v>
+      </c>
+      <c r="G14">
+        <v>10.778</v>
+      </c>
+      <c r="H14">
+        <v>106.7018</v>
+      </c>
+      <c r="I14" t="str">
+        <v>2026-05-12T08:41:15.945Z</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>test-addr-0901000011-0</v>
+      </c>
+      <c r="B15" t="str">
+        <v>0901000011</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Home</v>
+      </c>
+      <c r="D15" t="str">
+        <v>200 Lê Văn Sỹ, Phường 14, Quận 3</v>
+      </c>
+      <c r="E15" t="str">
+        <v>Q3</v>
+      </c>
+      <c r="F15" t="b">
+        <v>1</v>
+      </c>
+      <c r="G15">
+        <v>10.7939</v>
+      </c>
+      <c r="H15">
+        <v>106.6844</v>
+      </c>
+      <c r="I15" t="str">
+        <v>2026-05-12T08:41:15.945Z</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>test-addr-0901000012-0</v>
+      </c>
+      <c r="B16" t="str">
+        <v>0901000012</v>
+      </c>
+      <c r="C16" t="str">
+        <v>Home</v>
+      </c>
+      <c r="D16" t="str">
+        <v>45 Phan Xích Long, Phường 3, Phú Nhuận</v>
+      </c>
+      <c r="E16" t="str">
+        <v>PN</v>
+      </c>
+      <c r="F16" t="b">
+        <v>1</v>
+      </c>
+      <c r="G16">
+        <v>10.798</v>
+      </c>
+      <c r="H16">
+        <v>106.684</v>
+      </c>
+      <c r="I16" t="str">
+        <v>2026-05-12T08:41:15.945Z</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>test-addr-0901000013-0</v>
+      </c>
+      <c r="B17" t="str">
+        <v>0901000013</v>
+      </c>
+      <c r="C17" t="str">
+        <v>Home</v>
+      </c>
+      <c r="D17" t="str">
+        <v>9 Hoàng Văn Thụ, Phường 8, Phú Nhuận</v>
+      </c>
+      <c r="E17" t="str">
+        <v>PN</v>
+      </c>
+      <c r="F17" t="b">
+        <v>1</v>
+      </c>
+      <c r="G17">
+        <v>10.8009</v>
+      </c>
+      <c r="H17">
+        <v>106.6803</v>
+      </c>
+      <c r="I17" t="str">
+        <v>2026-05-12T08:41:15.945Z</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>test-addr-0901000013-1</v>
+      </c>
+      <c r="B18" t="str">
+        <v>0901000013</v>
+      </c>
+      <c r="C18" t="str">
+        <v>Office</v>
+      </c>
+      <c r="D18" t="str">
+        <v>100 Tô Ký, Phường Trung Mỹ Tây, Quận 12</v>
+      </c>
+      <c r="E18" t="str">
+        <v>Q12</v>
+      </c>
+      <c r="F18" t="b">
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <v>10.862</v>
+      </c>
+      <c r="H18">
+        <v>106.6411</v>
+      </c>
+      <c r="I18" t="str">
+        <v>2026-05-12T08:41:15.945Z</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>test-addr-0901000014-0</v>
+      </c>
+      <c r="B19" t="str">
+        <v>0901000014</v>
+      </c>
+      <c r="C19" t="str">
+        <v>Home</v>
+      </c>
+      <c r="D19" t="str">
+        <v>33 Nguyễn Trọng Tuyển, Phường 10, Phú Nhuận</v>
+      </c>
+      <c r="E19" t="str">
+        <v>PN</v>
+      </c>
+      <c r="F19" t="b">
+        <v>1</v>
+      </c>
+      <c r="G19">
+        <v>10.7952</v>
+      </c>
+      <c r="H19">
+        <v>106.6762</v>
+      </c>
+      <c r="I19" t="str">
+        <v>2026-05-12T08:41:15.945Z</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>test-addr-0901000015-0</v>
+      </c>
+      <c r="B20" t="str">
+        <v>0901000015</v>
+      </c>
+      <c r="C20" t="str">
+        <v>Home</v>
+      </c>
+      <c r="D20" t="str">
+        <v>120 Điện Biên Phủ, Phường 15, Bình Thạnh</v>
+      </c>
+      <c r="E20" t="str">
+        <v>BT</v>
+      </c>
+      <c r="F20" t="b">
+        <v>1</v>
+      </c>
+      <c r="G20">
+        <v>10.8051</v>
+      </c>
+      <c r="H20">
+        <v>106.7098</v>
+      </c>
+      <c r="I20" t="str">
+        <v>2026-05-12T08:41:15.945Z</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>test-addr-0901000016-0</v>
+      </c>
+      <c r="B21" t="str">
+        <v>0901000016</v>
+      </c>
+      <c r="C21" t="str">
+        <v>Home</v>
+      </c>
+      <c r="D21" t="str">
+        <v>55 Bạch Đằng, Phường 2, Bình Thạnh</v>
+      </c>
+      <c r="E21" t="str">
+        <v>BT</v>
+      </c>
+      <c r="F21" t="b">
+        <v>1</v>
+      </c>
+      <c r="G21">
+        <v>10.8011</v>
+      </c>
+      <c r="H21">
+        <v>106.7122</v>
+      </c>
+      <c r="I21" t="str">
+        <v>2026-05-12T08:41:15.945Z</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>test-addr-0901000017-0</v>
+      </c>
+      <c r="B22" t="str">
+        <v>0901000017</v>
+      </c>
+      <c r="C22" t="str">
+        <v>Home</v>
+      </c>
+      <c r="D22" t="str">
+        <v>72 Nguyễn Gia Trí, Phường 25, Bình Thạnh</v>
+      </c>
+      <c r="E22" t="str">
+        <v>BT</v>
+      </c>
+      <c r="F22" t="b">
+        <v>1</v>
+      </c>
+      <c r="G22">
+        <v>10.8089</v>
+      </c>
+      <c r="H22">
+        <v>106.7199</v>
+      </c>
+      <c r="I22" t="str">
+        <v>2026-05-12T08:41:15.945Z</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>test-addr-0901000017-1</v>
+      </c>
+      <c r="B23" t="str">
+        <v>0901000017</v>
+      </c>
+      <c r="C23" t="str">
+        <v>Office</v>
+      </c>
+      <c r="D23" t="str">
+        <v>12 Lê Văn Lương, Phước Kiểng, Nhà Bè</v>
+      </c>
+      <c r="E23" t="str">
+        <v>NB</v>
+      </c>
+      <c r="F23" t="b">
+        <v>0</v>
+      </c>
+      <c r="G23">
+        <v>10.6951</v>
+      </c>
+      <c r="H23">
+        <v>106.7221</v>
+      </c>
+      <c r="I23" t="str">
+        <v>2026-05-12T08:41:15.945Z</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>test-addr-0901000018-0</v>
+      </c>
+      <c r="B24" t="str">
+        <v>0901000018</v>
+      </c>
+      <c r="C24" t="str">
+        <v>Home</v>
+      </c>
+      <c r="D24" t="str">
+        <v>14 Hoàng Diệu, Phường 10, Quận 4</v>
+      </c>
+      <c r="E24" t="str">
+        <v>Q4</v>
+      </c>
+      <c r="F24" t="b">
+        <v>1</v>
+      </c>
+      <c r="G24">
+        <v>10.7611</v>
+      </c>
+      <c r="H24">
+        <v>106.7</v>
+      </c>
+      <c r="I24" t="str">
+        <v>2026-05-12T08:41:15.945Z</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>test-addr-0901000019-0</v>
+      </c>
+      <c r="B25" t="str">
+        <v>0901000019</v>
+      </c>
+      <c r="C25" t="str">
+        <v>Home</v>
+      </c>
+      <c r="D25" t="str">
+        <v>39 Tôn Thất Thuyết, Phường 16, Quận 4</v>
+      </c>
+      <c r="E25" t="str">
+        <v>Q4</v>
+      </c>
+      <c r="F25" t="b">
+        <v>1</v>
+      </c>
+      <c r="G25">
+        <v>10.7589</v>
+      </c>
+      <c r="H25">
+        <v>106.7012</v>
+      </c>
+      <c r="I25" t="str">
+        <v>2026-05-12T08:41:15.945Z</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>test-addr-0901000020-0</v>
+      </c>
+      <c r="B26" t="str">
+        <v>0901000020</v>
+      </c>
+      <c r="C26" t="str">
+        <v>Home</v>
+      </c>
+      <c r="D26" t="str">
+        <v>67 Trần Xuân Soạn, Phường Tân Kiểng, Quận 7</v>
+      </c>
+      <c r="E26" t="str">
+        <v>Q7</v>
+      </c>
+      <c r="F26" t="b">
+        <v>1</v>
+      </c>
+      <c r="G26">
+        <v>10.7481</v>
+      </c>
+      <c r="H26">
+        <v>106.71</v>
+      </c>
+      <c r="I26" t="str">
+        <v>2026-05-12T08:41:15.945Z</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>test-addr-0901000021-0</v>
+      </c>
+      <c r="B27" t="str">
+        <v>0901000021</v>
+      </c>
+      <c r="C27" t="str">
+        <v>Home</v>
+      </c>
+      <c r="D27" t="str">
+        <v>5 Lê Thánh Tôn, Phường Bến Nghé, Quận 1</v>
+      </c>
+      <c r="E27" t="str">
+        <v>Q1</v>
+      </c>
+      <c r="F27" t="b">
+        <v>1</v>
+      </c>
+      <c r="G27">
+        <v>10.776</v>
+      </c>
+      <c r="H27">
+        <v>106.7071</v>
+      </c>
+      <c r="I27" t="str">
+        <v>2026-05-12T08:41:15.945Z</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>test-addr-0901000021-1</v>
+      </c>
+      <c r="B28" t="str">
+        <v>0901000021</v>
+      </c>
+      <c r="C28" t="str">
+        <v>Office</v>
+      </c>
+      <c r="D28" t="str">
+        <v>12 Nguyễn Huệ, Bến Nghé, Quận 1</v>
+      </c>
+      <c r="E28" t="str">
+        <v>Q1</v>
+      </c>
+      <c r="F28" t="b">
+        <v>0</v>
+      </c>
+      <c r="G28">
+        <v>10.7737</v>
+      </c>
+      <c r="H28">
+        <v>106.7033</v>
+      </c>
+      <c r="I28" t="str">
+        <v>2026-05-12T08:41:15.945Z</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>test-addr-0901000022-0</v>
+      </c>
+      <c r="B29" t="str">
+        <v>0901000022</v>
+      </c>
+      <c r="C29" t="str">
+        <v>Home</v>
+      </c>
+      <c r="D29" t="str">
+        <v>200 Nguyễn Thị Minh Khai, Phường 6, Quận 3</v>
+      </c>
+      <c r="E29" t="str">
+        <v>Q3</v>
+      </c>
+      <c r="F29" t="b">
+        <v>1</v>
+      </c>
+      <c r="G29">
+        <v>10.7792</v>
+      </c>
+      <c r="H29">
+        <v>106.6905</v>
+      </c>
+      <c r="I29" t="str">
+        <v>2026-05-12T08:41:15.945Z</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>test-addr-0901000023-0</v>
+      </c>
+      <c r="B30" t="str">
+        <v>0901000023</v>
+      </c>
+      <c r="C30" t="str">
+        <v>Home</v>
+      </c>
+      <c r="D30" t="str">
+        <v>88 Cộng Hòa, Phường 4, Tân Bình</v>
+      </c>
+      <c r="E30" t="str">
+        <v>TB</v>
+      </c>
+      <c r="F30" t="b">
+        <v>1</v>
+      </c>
+      <c r="G30">
+        <v>10.8012</v>
+      </c>
+      <c r="H30">
+        <v>106.6522</v>
+      </c>
+      <c r="I30" t="str">
+        <v>2026-05-12T08:41:15.945Z</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>test-addr-0901000024-0</v>
+      </c>
+      <c r="B31" t="str">
+        <v>0901000024</v>
+      </c>
+      <c r="C31" t="str">
+        <v>Home</v>
+      </c>
+      <c r="D31" t="str">
+        <v>120 Trường Chinh, Phường 12, Tân Bình</v>
+      </c>
+      <c r="E31" t="str">
+        <v>TB</v>
+      </c>
+      <c r="F31" t="b">
+        <v>1</v>
+      </c>
+      <c r="G31">
+        <v>10.8155</v>
+      </c>
+      <c r="H31">
+        <v>106.6478</v>
+      </c>
+      <c r="I31" t="str">
+        <v>2026-05-12T08:41:15.945Z</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>test-addr-0901000025-0</v>
+      </c>
+      <c r="B32" t="str">
+        <v>0901000025</v>
+      </c>
+      <c r="C32" t="str">
+        <v>Home</v>
+      </c>
+      <c r="D32" t="str">
+        <v>44 Lê Trọng Tấn, Phường Tây Thạnh, Tân Phú</v>
+      </c>
+      <c r="E32" t="str">
+        <v>TP</v>
+      </c>
+      <c r="F32" t="b">
+        <v>1</v>
+      </c>
+      <c r="G32">
+        <v>10.79</v>
+      </c>
+      <c r="H32">
+        <v>106.63</v>
+      </c>
+      <c r="I32" t="str">
+        <v>2026-05-12T08:41:15.945Z</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>test-addr-0901000025-1</v>
+      </c>
+      <c r="B33" t="str">
+        <v>0901000025</v>
+      </c>
+      <c r="C33" t="str">
+        <v>Office</v>
+      </c>
+      <c r="D33" t="str">
+        <v>101 Lý Tự Trọng, Phường Bến Nghé, Quận 1</v>
+      </c>
+      <c r="E33" t="str">
+        <v>Q1</v>
+      </c>
+      <c r="F33" t="b">
+        <v>0</v>
+      </c>
+      <c r="G33">
+        <v>10.7752</v>
+      </c>
+      <c r="H33">
+        <v>106.7012</v>
+      </c>
+      <c r="I33" t="str">
+        <v>2026-05-12T08:41:15.945Z</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>test-addr-0901000026-0</v>
+      </c>
+      <c r="B34" t="str">
+        <v>0901000026</v>
+      </c>
+      <c r="C34" t="str">
+        <v>Home</v>
+      </c>
+      <c r="D34" t="str">
+        <v>66 Gò Vấp, Phường 3, Gò Vấp</v>
+      </c>
+      <c r="E34" t="str">
+        <v>GV</v>
+      </c>
+      <c r="F34" t="b">
+        <v>1</v>
+      </c>
+      <c r="G34">
+        <v>10.833</v>
+      </c>
+      <c r="H34">
+        <v>106.6832</v>
+      </c>
+      <c r="I34" t="str">
+        <v>2026-05-12T08:41:15.945Z</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>test-addr-0901000027-0</v>
+      </c>
+      <c r="B35" t="str">
+        <v>0901000027</v>
+      </c>
+      <c r="C35" t="str">
+        <v>Home</v>
+      </c>
+      <c r="D35" t="str">
+        <v>18 Phan Văn Trị, Phường 5, Gò Vấp</v>
+      </c>
+      <c r="E35" t="str">
+        <v>GV</v>
+      </c>
+      <c r="F35" t="b">
+        <v>1</v>
+      </c>
+      <c r="G35">
+        <v>10.827</v>
+      </c>
+      <c r="H35">
+        <v>106.6889</v>
+      </c>
+      <c r="I35" t="str">
+        <v>2026-05-12T08:41:15.945Z</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>test-addr-0901000028-0</v>
+      </c>
+      <c r="B36" t="str">
+        <v>0901000028</v>
+      </c>
+      <c r="C36" t="str">
+        <v>Home</v>
+      </c>
+      <c r="D36" t="str">
+        <v>90 Nguyễn Văn Nghi, Phường 7, Gò Vấp</v>
+      </c>
+      <c r="E36" t="str">
+        <v>GV</v>
+      </c>
+      <c r="F36" t="b">
+        <v>1</v>
+      </c>
+      <c r="G36">
+        <v>10.8199</v>
+      </c>
+      <c r="H36">
+        <v>106.6811</v>
+      </c>
+      <c r="I36" t="str">
+        <v>2026-05-12T08:41:15.945Z</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>test-addr-0901000029-0</v>
+      </c>
+      <c r="B37" t="str">
+        <v>0901000029</v>
+      </c>
+      <c r="C37" t="str">
+        <v>Home</v>
+      </c>
+      <c r="D37" t="str">
+        <v>15 Nguyễn Thị Thập, Phường Tân Phú, Quận 7</v>
+      </c>
+      <c r="E37" t="str">
+        <v>Q7</v>
+      </c>
+      <c r="F37" t="b">
+        <v>1</v>
+      </c>
+      <c r="G37">
+        <v>10.731</v>
+      </c>
+      <c r="H37">
+        <v>106.705</v>
+      </c>
+      <c r="I37" t="str">
+        <v>2026-05-12T08:41:15.945Z</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>test-addr-0901000029-1</v>
+      </c>
+      <c r="B38" t="str">
+        <v>0901000029</v>
+      </c>
+      <c r="C38" t="str">
+        <v>Office</v>
+      </c>
+      <c r="D38" t="str">
+        <v>30 Tôn Đức Thắng, Bến Nghé, Quận 1</v>
+      </c>
+      <c r="E38" t="str">
+        <v>Q1</v>
+      </c>
+      <c r="F38" t="b">
+        <v>0</v>
+      </c>
+      <c r="G38">
+        <v>10.7714</v>
+      </c>
+      <c r="H38">
+        <v>106.7052</v>
+      </c>
+      <c r="I38" t="str">
+        <v>2026-05-12T08:41:15.945Z</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>test-addr-0901000030-0</v>
+      </c>
+      <c r="B39" t="str">
+        <v>0901000030</v>
+      </c>
+      <c r="C39" t="str">
+        <v>Home</v>
+      </c>
+      <c r="D39" t="str">
+        <v>30 Huỳnh Tấn Phát, Phường Phú Thuận, Quận 7</v>
+      </c>
+      <c r="E39" t="str">
+        <v>Q7</v>
+      </c>
+      <c r="F39" t="b">
+        <v>1</v>
+      </c>
+      <c r="G39">
+        <v>10.726</v>
+      </c>
+      <c r="H39">
+        <v>106.712</v>
+      </c>
+      <c r="I39" t="str">
+        <v>2026-05-12T08:41:15.945Z</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>test-addr-0901000031-0</v>
+      </c>
+      <c r="B40" t="str">
+        <v>0901000031</v>
+      </c>
+      <c r="C40" t="str">
+        <v>Home</v>
+      </c>
+      <c r="D40" t="str">
+        <v>45 Lý Chiêu Hoàng, Phường 10, Quận 6</v>
+      </c>
+      <c r="E40" t="str">
+        <v>Q6</v>
+      </c>
+      <c r="F40" t="b">
+        <v>1</v>
+      </c>
+      <c r="G40">
+        <v>10.753</v>
+      </c>
+      <c r="H40">
+        <v>106.638</v>
+      </c>
+      <c r="I40" t="str">
+        <v>2026-05-12T08:41:15.945Z</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>test-addr-0901000032-0</v>
+      </c>
+      <c r="B41" t="str">
+        <v>0901000032</v>
+      </c>
+      <c r="C41" t="str">
+        <v>Home</v>
+      </c>
+      <c r="D41" t="str">
+        <v>77 Hậu Giang, Phường 11, Quận 6</v>
+      </c>
+      <c r="E41" t="str">
+        <v>Q6</v>
+      </c>
+      <c r="F41" t="b">
+        <v>1</v>
+      </c>
+      <c r="G41">
+        <v>10.748</v>
+      </c>
+      <c r="H41">
+        <v>106.642</v>
+      </c>
+      <c r="I41" t="str">
+        <v>2026-05-12T08:41:15.945Z</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>test-addr-0901000033-0</v>
+      </c>
+      <c r="B42" t="str">
+        <v>0901000033</v>
+      </c>
+      <c r="C42" t="str">
+        <v>Home</v>
+      </c>
+      <c r="D42" t="str">
+        <v>100 Tô Ký, Phường Trung Mỹ Tây, Quận 12</v>
+      </c>
+      <c r="E42" t="str">
+        <v>Q12</v>
+      </c>
+      <c r="F42" t="b">
+        <v>1</v>
+      </c>
+      <c r="G42">
+        <v>10.862</v>
+      </c>
+      <c r="H42">
+        <v>106.6411</v>
+      </c>
+      <c r="I42" t="str">
+        <v>2026-05-12T08:41:15.945Z</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>test-addr-0901000033-1</v>
+      </c>
+      <c r="B43" t="str">
+        <v>0901000033</v>
+      </c>
+      <c r="C43" t="str">
+        <v>Office</v>
+      </c>
+      <c r="D43" t="str">
+        <v>9 Hoàng Văn Thụ, Phường 8, Phú Nhuận</v>
+      </c>
+      <c r="E43" t="str">
+        <v>PN</v>
+      </c>
+      <c r="F43" t="b">
+        <v>0</v>
+      </c>
+      <c r="G43">
+        <v>10.8009</v>
+      </c>
+      <c r="H43">
+        <v>106.6803</v>
+      </c>
+      <c r="I43" t="str">
+        <v>2026-05-12T08:41:15.945Z</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>test-addr-0901000034-0</v>
+      </c>
+      <c r="B44" t="str">
+        <v>0901000034</v>
+      </c>
+      <c r="C44" t="str">
+        <v>Home</v>
+      </c>
+      <c r="D44" t="str">
+        <v>55 Hà Huy Giáp, Phường Thạnh Lộc, Quận 12</v>
+      </c>
+      <c r="E44" t="str">
+        <v>Q12</v>
+      </c>
+      <c r="F44" t="b">
+        <v>1</v>
+      </c>
+      <c r="G44">
+        <v>10.8701</v>
+      </c>
+      <c r="H44">
+        <v>106.653</v>
+      </c>
+      <c r="I44" t="str">
+        <v>2026-05-12T08:41:15.945Z</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>test-addr-0901000035-0</v>
+      </c>
+      <c r="B45" t="str">
+        <v>0901000035</v>
+      </c>
+      <c r="C45" t="str">
+        <v>Home</v>
+      </c>
+      <c r="D45" t="str">
+        <v>23 Lê Văn Việt, Phường Hiệp Phú, Thủ Đức</v>
+      </c>
+      <c r="E45" t="str">
+        <v>TD</v>
+      </c>
+      <c r="F45" t="b">
+        <v>1</v>
+      </c>
+      <c r="G45">
+        <v>10.845</v>
+      </c>
+      <c r="H45">
+        <v>106.772</v>
+      </c>
+      <c r="I45" t="str">
+        <v>2026-05-12T08:41:15.945Z</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>test-addr-0901000036-0</v>
+      </c>
+      <c r="B46" t="str">
+        <v>0901000036</v>
+      </c>
+      <c r="C46" t="str">
+        <v>Home</v>
+      </c>
+      <c r="D46" t="str">
+        <v>88 Võ Văn Ngân, Phường Bình Thọ, Thủ Đức</v>
+      </c>
+      <c r="E46" t="str">
+        <v>TD</v>
+      </c>
+      <c r="F46" t="b">
+        <v>1</v>
+      </c>
+      <c r="G46">
+        <v>10.8519</v>
+      </c>
+      <c r="H46">
+        <v>106.7601</v>
+      </c>
+      <c r="I46" t="str">
+        <v>2026-05-12T08:41:15.945Z</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>test-addr-0901000037-0</v>
+      </c>
+      <c r="B47" t="str">
+        <v>0901000037</v>
+      </c>
+      <c r="C47" t="str">
+        <v>Home</v>
+      </c>
+      <c r="D47" t="str">
+        <v>12 Lê Văn Lương, Phước Kiểng, Nhà Bè</v>
+      </c>
+      <c r="E47" t="str">
+        <v>NB</v>
+      </c>
+      <c r="F47" t="b">
+        <v>1</v>
+      </c>
+      <c r="G47">
+        <v>10.6951</v>
+      </c>
+      <c r="H47">
+        <v>106.7221</v>
+      </c>
+      <c r="I47" t="str">
+        <v>2026-05-12T08:41:15.945Z</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>test-addr-0901000037-1</v>
+      </c>
+      <c r="B48" t="str">
+        <v>0901000037</v>
+      </c>
+      <c r="C48" t="str">
+        <v>Office</v>
+      </c>
+      <c r="D48" t="str">
+        <v>72 Nguyễn Gia Trí, Phường 25, Bình Thạnh</v>
+      </c>
+      <c r="E48" t="str">
+        <v>BT</v>
+      </c>
+      <c r="F48" t="b">
+        <v>0</v>
+      </c>
+      <c r="G48">
+        <v>10.8089</v>
+      </c>
+      <c r="H48">
+        <v>106.7199</v>
+      </c>
+      <c r="I48" t="str">
+        <v>2026-05-12T08:41:15.945Z</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>test-addr-0901000038-0</v>
+      </c>
+      <c r="B49" t="str">
+        <v>0901000038</v>
+      </c>
+      <c r="C49" t="str">
+        <v>Home</v>
+      </c>
+      <c r="D49" t="str">
+        <v>34 Nguyễn Hữu Thọ, Phường Tân Hưng, Quận 7</v>
+      </c>
+      <c r="E49" t="str">
+        <v>Q7</v>
+      </c>
+      <c r="F49" t="b">
+        <v>1</v>
+      </c>
+      <c r="G49">
+        <v>10.715</v>
+      </c>
+      <c r="H49">
+        <v>106.702</v>
+      </c>
+      <c r="I49" t="str">
+        <v>2026-05-12T08:41:15.945Z</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>test-addr-0901000039-0</v>
+      </c>
+      <c r="B50" t="str">
+        <v>0901000039</v>
+      </c>
+      <c r="C50" t="str">
+        <v>Home</v>
+      </c>
+      <c r="D50" t="str">
+        <v>90 An Dương Vương, Phường An Lạc, Bình Tân</v>
+      </c>
+      <c r="E50" t="str">
+        <v>BTan</v>
+      </c>
+      <c r="F50" t="b">
+        <v>1</v>
+      </c>
+      <c r="G50">
+        <v>10.753</v>
+      </c>
+      <c r="H50">
+        <v>106.605</v>
+      </c>
+      <c r="I50" t="str">
+        <v>2026-05-12T08:41:15.945Z</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>test-addr-0901000040-0</v>
+      </c>
+      <c r="B51" t="str">
+        <v>0901000040</v>
+      </c>
+      <c r="C51" t="str">
+        <v>Home</v>
+      </c>
+      <c r="D51" t="str">
+        <v>120 Kinh Dương Vương, Phường 12, Bình Tân</v>
+      </c>
+      <c r="E51" t="str">
+        <v>BTan</v>
+      </c>
+      <c r="F51" t="b">
+        <v>1</v>
+      </c>
+      <c r="G51">
+        <v>10.7489</v>
+      </c>
+      <c r="H51">
+        <v>106.6</v>
+      </c>
+      <c r="I51" t="str">
+        <v>2026-05-12T08:41:15.945Z</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>test-addr-0901000041-0</v>
+      </c>
+      <c r="B52" t="str">
+        <v>0901000041</v>
+      </c>
+      <c r="C52" t="str">
+        <v>Home</v>
+      </c>
+      <c r="D52" t="str">
+        <v>12 Nguyễn Huệ, Bến Nghé, Quận 1</v>
+      </c>
+      <c r="E52" t="str">
+        <v>Q1</v>
+      </c>
+      <c r="F52" t="b">
+        <v>1</v>
+      </c>
+      <c r="G52">
+        <v>10.7737</v>
+      </c>
+      <c r="H52">
+        <v>106.7033</v>
+      </c>
+      <c r="I52" t="str">
+        <v>2026-05-12T08:41:15.945Z</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>test-addr-0901000041-1</v>
+      </c>
+      <c r="B53" t="str">
+        <v>0901000041</v>
+      </c>
+      <c r="C53" t="str">
+        <v>Office</v>
+      </c>
+      <c r="D53" t="str">
+        <v>5 Lê Thánh Tôn, Phường Bến Nghé, Quận 1</v>
+      </c>
+      <c r="E53" t="str">
+        <v>Q1</v>
+      </c>
+      <c r="F53" t="b">
+        <v>0</v>
+      </c>
+      <c r="G53">
+        <v>10.776</v>
+      </c>
+      <c r="H53">
+        <v>106.7071</v>
+      </c>
+      <c r="I53" t="str">
+        <v>2026-05-12T08:41:15.945Z</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>test-addr-0901000042-0</v>
+      </c>
+      <c r="B54" t="str">
+        <v>0901000042</v>
+      </c>
+      <c r="C54" t="str">
+        <v>Home</v>
+      </c>
+      <c r="D54" t="str">
+        <v>56 Lê Lợi, Phường Bến Thành, Quận 1</v>
+      </c>
+      <c r="E54" t="str">
+        <v>Q1</v>
+      </c>
+      <c r="F54" t="b">
+        <v>1</v>
+      </c>
+      <c r="G54">
+        <v>10.7726</v>
+      </c>
+      <c r="H54">
+        <v>106.6981</v>
+      </c>
+      <c r="I54" t="str">
+        <v>2026-05-12T08:41:15.945Z</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>test-addr-0901000043-0</v>
+      </c>
+      <c r="B55" t="str">
+        <v>0901000043</v>
+      </c>
+      <c r="C55" t="str">
+        <v>Home</v>
+      </c>
+      <c r="D55" t="str">
+        <v>78 Đinh Tiên Hoàng, Phường Đa Kao, Quận 1</v>
+      </c>
+      <c r="E55" t="str">
+        <v>Q1</v>
+      </c>
+      <c r="F55" t="b">
+        <v>1</v>
+      </c>
+      <c r="G55">
+        <v>10.7869</v>
+      </c>
+      <c r="H55">
+        <v>106.7009</v>
+      </c>
+      <c r="I55" t="str">
+        <v>2026-05-12T08:41:15.945Z</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>test-addr-0901000044-0</v>
+      </c>
+      <c r="B56" t="str">
+        <v>0901000044</v>
+      </c>
+      <c r="C56" t="str">
+        <v>Home</v>
+      </c>
+      <c r="D56" t="str">
+        <v>34 Trần Hưng Đạo, Phường Nguyễn Cư Trinh, Quận 1</v>
+      </c>
+      <c r="E56" t="str">
+        <v>Q1</v>
+      </c>
+      <c r="F56" t="b">
+        <v>1</v>
+      </c>
+      <c r="G56">
+        <v>10.766</v>
+      </c>
+      <c r="H56">
+        <v>106.6961</v>
+      </c>
+      <c r="I56" t="str">
+        <v>2026-05-12T08:41:15.945Z</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>test-addr-0901000045-0</v>
+      </c>
+      <c r="B57" t="str">
+        <v>0901000045</v>
+      </c>
+      <c r="C57" t="str">
+        <v>Home</v>
+      </c>
+      <c r="D57" t="str">
+        <v>101 Lý Tự Trọng, Phường Bến Nghé, Quận 1</v>
+      </c>
+      <c r="E57" t="str">
+        <v>Q1</v>
+      </c>
+      <c r="F57" t="b">
+        <v>1</v>
+      </c>
+      <c r="G57">
+        <v>10.7752</v>
+      </c>
+      <c r="H57">
+        <v>106.7012</v>
+      </c>
+      <c r="I57" t="str">
+        <v>2026-05-12T08:41:15.945Z</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>test-addr-0901000045-1</v>
+      </c>
+      <c r="B58" t="str">
+        <v>0901000045</v>
+      </c>
+      <c r="C58" t="str">
+        <v>Office</v>
+      </c>
+      <c r="D58" t="str">
+        <v>44 Lê Trọng Tấn, Phường Tây Thạnh, Tân Phú</v>
+      </c>
+      <c r="E58" t="str">
+        <v>TP</v>
+      </c>
+      <c r="F58" t="b">
+        <v>0</v>
+      </c>
+      <c r="G58">
+        <v>10.79</v>
+      </c>
+      <c r="H58">
+        <v>106.63</v>
+      </c>
+      <c r="I58" t="str">
+        <v>2026-05-12T08:41:15.945Z</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>test-addr-0901000046-0</v>
+      </c>
+      <c r="B59" t="str">
+        <v>0901000046</v>
+      </c>
+      <c r="C59" t="str">
+        <v>Home</v>
+      </c>
+      <c r="D59" t="str">
+        <v>22 Võ Thị Sáu, Phường 7, Quận 3</v>
+      </c>
+      <c r="E59" t="str">
+        <v>Q3</v>
+      </c>
+      <c r="F59" t="b">
+        <v>1</v>
+      </c>
+      <c r="G59">
+        <v>10.7845</v>
+      </c>
+      <c r="H59">
+        <v>106.6892</v>
+      </c>
+      <c r="I59" t="str">
+        <v>2026-05-12T08:41:15.945Z</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>test-addr-0901000047-0</v>
+      </c>
+      <c r="B60" t="str">
+        <v>0901000047</v>
+      </c>
+      <c r="C60" t="str">
+        <v>Home</v>
+      </c>
+      <c r="D60" t="str">
+        <v>88 Nam Kỳ Khởi Nghĩa, Phường 8, Quận 3</v>
+      </c>
+      <c r="E60" t="str">
+        <v>Q3</v>
+      </c>
+      <c r="F60" t="b">
+        <v>1</v>
+      </c>
+      <c r="G60">
+        <v>10.7804</v>
+      </c>
+      <c r="H60">
+        <v>106.6878</v>
+      </c>
+      <c r="I60" t="str">
+        <v>2026-05-12T08:41:15.945Z</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>test-addr-0901000048-0</v>
+      </c>
+      <c r="B61" t="str">
+        <v>0901000048</v>
+      </c>
+      <c r="C61" t="str">
+        <v>Home</v>
+      </c>
+      <c r="D61" t="str">
+        <v>15 Nguyễn Đình Chiểu, Phường 1, Quận 3</v>
+      </c>
+      <c r="E61" t="str">
+        <v>Q3</v>
+      </c>
+      <c r="F61" t="b">
+        <v>1</v>
+      </c>
+      <c r="G61">
+        <v>10.7763</v>
+      </c>
+      <c r="H61">
+        <v>106.693</v>
+      </c>
+      <c r="I61" t="str">
+        <v>2026-05-12T08:41:15.945Z</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>test-addr-0901000049-0</v>
+      </c>
+      <c r="B62" t="str">
+        <v>0901000049</v>
+      </c>
+      <c r="C62" t="str">
+        <v>Home</v>
+      </c>
+      <c r="D62" t="str">
+        <v>30 Tôn Đức Thắng, Bến Nghé, Quận 1</v>
+      </c>
+      <c r="E62" t="str">
+        <v>Q1</v>
+      </c>
+      <c r="F62" t="b">
+        <v>1</v>
+      </c>
+      <c r="G62">
+        <v>10.7714</v>
+      </c>
+      <c r="H62">
+        <v>106.7052</v>
+      </c>
+      <c r="I62" t="str">
+        <v>2026-05-12T08:41:15.945Z</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>test-addr-0901000049-1</v>
+      </c>
+      <c r="B63" t="str">
+        <v>0901000049</v>
+      </c>
+      <c r="C63" t="str">
+        <v>Office</v>
+      </c>
+      <c r="D63" t="str">
+        <v>15 Nguyễn Thị Thập, Phường Tân Phú, Quận 7</v>
+      </c>
+      <c r="E63" t="str">
+        <v>Q7</v>
+      </c>
+      <c r="F63" t="b">
+        <v>0</v>
+      </c>
+      <c r="G63">
+        <v>10.731</v>
+      </c>
+      <c r="H63">
+        <v>106.705</v>
+      </c>
+      <c r="I63" t="str">
+        <v>2026-05-12T08:41:15.945Z</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>test-addr-0901000050-0</v>
+      </c>
+      <c r="B64" t="str">
+        <v>0901000050</v>
+      </c>
+      <c r="C64" t="str">
+        <v>Home</v>
+      </c>
+      <c r="D64" t="str">
+        <v>8 Hai Bà Trưng, Bến Nghé, Quận 1</v>
+      </c>
+      <c r="E64" t="str">
+        <v>Q1</v>
+      </c>
+      <c r="F64" t="b">
+        <v>1</v>
+      </c>
+      <c r="G64">
+        <v>10.778</v>
+      </c>
+      <c r="H64">
+        <v>106.7018</v>
+      </c>
+      <c r="I64" t="str">
+        <v>2026-05-12T08:41:15.945Z</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I64"/>
   </ignoredErrors>
 </worksheet>
 </file>